--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_ZENTRO BASKET MADRID.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_ZENTRO BASKET MADRID.xlsx
@@ -565,67 +565,67 @@
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>13.1294</v>
+        <v>13.0654</v>
       </c>
       <c r="E2" t="n">
-        <v>8.985099999999999</v>
+        <v>9.3726</v>
       </c>
       <c r="F2" t="n">
-        <v>4.144299999999999</v>
+        <v>3.6928</v>
       </c>
       <c r="G2" t="n">
-        <v>4.454899999999999</v>
+        <v>4.5343</v>
       </c>
       <c r="H2" t="n">
-        <v>3.8138</v>
+        <v>3.9658</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6411</v>
+        <v>0.5685</v>
       </c>
       <c r="J2" t="n">
-        <v>2.8301</v>
+        <v>3.092000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>2.6301</v>
+        <v>2.8893</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2</v>
+        <v>0.2026</v>
       </c>
       <c r="M2" t="n">
-        <v>1.6248</v>
+        <v>1.4423</v>
       </c>
       <c r="N2" t="n">
-        <v>1.1837</v>
+        <v>1.0764</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4411</v>
+        <v>0.3659</v>
       </c>
       <c r="P2" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="S2" t="n">
-        <v>4.9546</v>
+        <v>4.8037</v>
       </c>
       <c r="T2" t="n">
-        <v>2.4566</v>
+        <v>2.4412</v>
       </c>
       <c r="U2" t="n">
-        <v>2.498</v>
+        <v>2.3626</v>
       </c>
       <c r="V2" t="n">
-        <v>1.7194</v>
+        <v>1.78</v>
       </c>
       <c r="W2" t="n">
-        <v>3.6985</v>
+        <v>3.8395</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.9791</v>
+        <v>-2.0595</v>
       </c>
     </row>
     <row r="3">
@@ -643,58 +643,58 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5843</v>
+        <v>2.5444</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4285</v>
+        <v>1.4772</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1558</v>
+        <v>1.0672</v>
       </c>
       <c r="G3" t="n">
-        <v>2.2427</v>
+        <v>2.2167</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8779</v>
+        <v>0.8697</v>
       </c>
       <c r="I3" t="n">
-        <v>1.3648</v>
+        <v>1.3469</v>
       </c>
       <c r="J3" t="n">
-        <v>1.6796</v>
+        <v>1.7153</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9997</v>
+        <v>1.0264</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6799000000000001</v>
+        <v>0.6889</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5630999999999999</v>
+        <v>0.5014000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1218</v>
+        <v>-0.1565</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6849000000000001</v>
+        <v>0.6579</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6002000000000001</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8002</v>
+        <v>0.779</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2585</v>
+        <v>-0.2565</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.05110000000000001</v>
+        <v>-0.04340000000000002</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2075</v>
+        <v>-0.2131</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,67 +721,67 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4236</v>
+        <v>2.2298</v>
       </c>
       <c r="E4" t="n">
-        <v>0.415</v>
+        <v>0.7176999999999998</v>
       </c>
       <c r="F4" t="n">
-        <v>2.0086</v>
+        <v>1.5122</v>
       </c>
       <c r="G4" t="n">
-        <v>2.5347</v>
+        <v>2.4491</v>
       </c>
       <c r="H4" t="n">
-        <v>1.3299</v>
+        <v>1.2643</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2048</v>
+        <v>1.1848</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1327</v>
+        <v>1.3553</v>
       </c>
       <c r="K4" t="n">
-        <v>2.4029</v>
+        <v>2.5299</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.2703</v>
+        <v>-1.1746</v>
       </c>
       <c r="M4" t="n">
-        <v>1.402</v>
+        <v>1.0937</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.0731</v>
+        <v>-1.2656</v>
       </c>
       <c r="O4" t="n">
-        <v>2.4751</v>
+        <v>2.3594</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.6001000000000001</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.0009</v>
+        <v>-2.9211</v>
       </c>
       <c r="R4" t="n">
-        <v>2.4006</v>
+        <v>2.3368</v>
       </c>
       <c r="S4" t="n">
-        <v>2.5487</v>
+        <v>2.476</v>
       </c>
       <c r="T4" t="n">
-        <v>2.2833</v>
+        <v>2.2834</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2655</v>
+        <v>0.1927</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.0595</v>
+        <v>-2.1111</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.0595</v>
+        <v>-2.1111</v>
       </c>
     </row>
     <row r="5">
@@ -799,58 +799,58 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6411</v>
+        <v>1.6898</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.0217</v>
+        <v>-0.6441000000000003</v>
       </c>
       <c r="F5" t="n">
-        <v>2.6628</v>
+        <v>2.334</v>
       </c>
       <c r="G5" t="n">
-        <v>3.4025</v>
+        <v>3.3993</v>
       </c>
       <c r="H5" t="n">
-        <v>5.0989</v>
+        <v>5.0328</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.6965</v>
+        <v>-1.6336</v>
       </c>
       <c r="J5" t="n">
-        <v>1.6143</v>
+        <v>1.8819</v>
       </c>
       <c r="K5" t="n">
-        <v>4.958600000000001</v>
+        <v>5.0906</v>
       </c>
       <c r="L5" t="n">
-        <v>-3.3443</v>
+        <v>-3.2087</v>
       </c>
       <c r="M5" t="n">
-        <v>1.7882</v>
+        <v>1.5175</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1404000000000001</v>
+        <v>-0.05769999999999997</v>
       </c>
       <c r="O5" t="n">
-        <v>1.6478</v>
+        <v>1.5751</v>
       </c>
       <c r="P5" t="n">
-        <v>0.8003</v>
+        <v>0.779</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.2007</v>
+        <v>-2.1421</v>
       </c>
       <c r="R5" t="n">
-        <v>3.0008</v>
+        <v>2.921</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.5616</v>
+        <v>-2.4884</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4354000000000001</v>
+        <v>-0.3838999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>-2.1261</v>
+        <v>-2.1044</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,31 +877,31 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1997</v>
+        <v>1.2237</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1997</v>
+        <v>1.2237</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1997</v>
+        <v>1.2237</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5998</v>
+        <v>0.6158</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1997</v>
+        <v>1.2237</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5998</v>
+        <v>0.6158</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -955,67 +955,67 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8874</v>
+        <v>0.9129</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9373</v>
+        <v>1.4249</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.05000000000000004</v>
+        <v>-0.512</v>
       </c>
       <c r="G7" t="n">
-        <v>4.2715</v>
+        <v>4.259</v>
       </c>
       <c r="H7" t="n">
-        <v>2.5088</v>
+        <v>2.5314</v>
       </c>
       <c r="I7" t="n">
-        <v>1.7628</v>
+        <v>1.7277</v>
       </c>
       <c r="J7" t="n">
-        <v>4.6898</v>
+        <v>4.9772</v>
       </c>
       <c r="K7" t="n">
-        <v>4.0461</v>
+        <v>4.2799</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6437</v>
+        <v>0.6972999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4182</v>
+        <v>-0.7181000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.5373</v>
+        <v>-1.7485</v>
       </c>
       <c r="O7" t="n">
-        <v>1.1191</v>
+        <v>1.0304</v>
       </c>
       <c r="P7" t="n">
-        <v>-3.2009</v>
+        <v>-3.1157</v>
       </c>
       <c r="Q7" t="n">
-        <v>-5.0014</v>
+        <v>-4.868399999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8006</v>
+        <v>1.7526</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6839999999999999</v>
+        <v>-0.6646000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>0.04919999999999999</v>
+        <v>0.09509999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7332000000000001</v>
+        <v>-0.7596999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5007</v>
+        <v>0.4342</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6990999999999999</v>
+        <v>-0.7868000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -1033,58 +1033,58 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1205</v>
+        <v>-1.1084</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.1546</v>
+        <v>-2.0432</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0341</v>
+        <v>0.9347</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2670000000000001</v>
+        <v>0.2424</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0148</v>
+        <v>-0.06569999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2819</v>
+        <v>0.3081</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5741999999999999</v>
+        <v>-0.513</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.578</v>
+        <v>-0.5619000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0038</v>
+        <v>0.0489</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8412000000000002</v>
+        <v>0.7554000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5631999999999999</v>
+        <v>0.4961</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2781000000000001</v>
+        <v>0.2592</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.4001</v>
+        <v>-0.3895000000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6002000000000001</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9874000000000001</v>
+        <v>-0.9613</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5800999999999999</v>
+        <v>-0.5565</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4073</v>
+        <v>-0.4048</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,67 +1111,67 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6103</v>
+        <v>-1.6463</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.5262</v>
+        <v>-1.9801</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9157000000000001</v>
+        <v>0.3336999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7743</v>
+        <v>-0.7081999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>-4.3574</v>
+        <v>-4.2399</v>
       </c>
       <c r="I9" t="n">
-        <v>3.5831</v>
+        <v>3.5317</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.034</v>
+        <v>-0.6546999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.9556</v>
+        <v>-2.6243</v>
       </c>
       <c r="L9" t="n">
-        <v>1.9216</v>
+        <v>1.9697</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2598</v>
+        <v>-0.05360000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.4018</v>
+        <v>-1.6156</v>
       </c>
       <c r="O9" t="n">
-        <v>1.6615</v>
+        <v>1.562</v>
       </c>
       <c r="P9" t="n">
-        <v>0.8002</v>
+        <v>0.779</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.2006</v>
+        <v>-2.1421</v>
       </c>
       <c r="R9" t="n">
-        <v>3.0008</v>
+        <v>2.921</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9373</v>
+        <v>-0.9300999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7510000000000001</v>
+        <v>-0.6839000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1863</v>
+        <v>-0.2463</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6989999999999998</v>
+        <v>-0.7869000000000002</v>
       </c>
       <c r="W9" t="n">
-        <v>1.4596</v>
+        <v>1.5006</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.1586</v>
+        <v>-2.2873</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0829</v>
+        <v>-1.9625</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.7935</v>
+        <v>-3.1695</v>
       </c>
       <c r="F10" t="n">
-        <v>1.7106</v>
+        <v>1.207</v>
       </c>
       <c r="G10" t="n">
-        <v>2.6691</v>
+        <v>2.6598</v>
       </c>
       <c r="H10" t="n">
-        <v>1.4411</v>
+        <v>1.3659</v>
       </c>
       <c r="I10" t="n">
-        <v>1.228</v>
+        <v>1.2939</v>
       </c>
       <c r="J10" t="n">
-        <v>1.1821</v>
+        <v>1.5238</v>
       </c>
       <c r="K10" t="n">
-        <v>2.1648</v>
+        <v>2.317</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.9826999999999999</v>
+        <v>-0.7932000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>1.4871</v>
+        <v>1.136</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7237</v>
+        <v>-0.9510999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>2.2107</v>
+        <v>2.0871</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.0009</v>
+        <v>-2.921</v>
       </c>
       <c r="Q10" t="n">
-        <v>-5.2014</v>
+        <v>-5.0631</v>
       </c>
       <c r="R10" t="n">
-        <v>2.2006</v>
+        <v>2.1421</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.3511</v>
+        <v>-2.3118</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.4934</v>
+        <v>-1.4102</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.8576</v>
+        <v>-0.9015000000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>0.5999</v>
+        <v>0.6104999999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>1.7194</v>
+        <v>1.78</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.1195</v>
+        <v>-1.1695</v>
       </c>
     </row>
     <row r="11">
@@ -1267,73 +1267,73 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.3375</v>
+        <v>-2.383</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7507</v>
+        <v>-1.5821</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5869</v>
+        <v>-0.8008999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1372</v>
+        <v>-0.1853000000000002</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.2042</v>
+        <v>-3.239</v>
       </c>
       <c r="I11" t="n">
-        <v>3.067</v>
+        <v>3.0538</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.5924</v>
+        <v>-0.5011000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.0322</v>
+        <v>-1.9601</v>
       </c>
       <c r="L11" t="n">
-        <v>1.4398</v>
+        <v>1.459</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4552</v>
+        <v>0.316</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.172</v>
+        <v>-1.2788</v>
       </c>
       <c r="O11" t="n">
-        <v>1.6272</v>
+        <v>1.5948</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.4001</v>
+        <v>-0.3895000000000001</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.2004</v>
+        <v>-1.1684</v>
       </c>
       <c r="R11" t="n">
-        <v>0.8002</v>
+        <v>0.779</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6004</v>
+        <v>-0.5872000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2177</v>
+        <v>-0.192</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3827</v>
+        <v>-0.3953</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.1998</v>
+        <v>-1.221</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.4596</v>
+        <v>-1.5005</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>N. VINO LOPEZ</t>
+          <t>J. VAQUERO PASCUAL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.5309</v>
+        <v>-2.5302</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.9192</v>
+        <v>-4.3917</v>
       </c>
       <c r="F12" t="n">
-        <v>1.3883</v>
+        <v>1.8614</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.2996</v>
+        <v>-1.1993</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.0833</v>
+        <v>-0.3273999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.2163</v>
+        <v>-0.8719</v>
       </c>
       <c r="J12" t="n">
-        <v>-4.1044</v>
+        <v>-0.5482</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.1964</v>
+        <v>2.158</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.908</v>
+        <v>-2.7063</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1952</v>
+        <v>-0.651</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8869</v>
+        <v>-2.4854</v>
       </c>
       <c r="O12" t="n">
-        <v>0.6917</v>
+        <v>1.8344</v>
       </c>
       <c r="P12" t="n">
-        <v>0.6001000000000001</v>
+        <v>2.1421</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.0006</v>
+        <v>-0.9737</v>
       </c>
       <c r="R12" t="n">
-        <v>2.6007</v>
+        <v>3.1158</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.291</v>
+        <v>-2.5315</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7332999999999998</v>
+        <v>-2.2076</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4423</v>
+        <v>-0.3238</v>
       </c>
       <c r="V12" t="n">
-        <v>1.4596</v>
+        <v>-0.9416</v>
       </c>
       <c r="W12" t="n">
-        <v>2.9191</v>
+        <v>-0.6621</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.4596</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. VAQUERO PASCUAL</t>
+          <t>N. VINO LOPEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.5658</v>
+        <v>-2.5544</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.8653</v>
+        <v>-3.5963</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2996</v>
+        <v>1.0419</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.2316</v>
+        <v>-4.348800000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.3310999999999999</v>
+        <v>-1.1752</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.9004000000000001</v>
+        <v>-3.1735</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.8778</v>
+        <v>-3.9634</v>
       </c>
       <c r="K13" t="n">
-        <v>1.9485</v>
+        <v>-0.1385</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.8263</v>
+        <v>-3.8249</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.3538</v>
+        <v>-0.3853</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.2797</v>
+        <v>-1.0367</v>
       </c>
       <c r="O13" t="n">
-        <v>1.9258</v>
+        <v>0.6514</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2007</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.0003</v>
+        <v>-1.9474</v>
       </c>
       <c r="R13" t="n">
-        <v>3.2009</v>
+        <v>2.5316</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.5947</v>
+        <v>-0.2905</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.3071</v>
+        <v>-0.6866</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2878</v>
+        <v>0.3962</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.9399999999999999</v>
+        <v>1.5005</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.6802</v>
+        <v>3.0011</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.2598</v>
+        <v>-1.5005</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.797400000000001</v>
+        <v>-5.7502</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.7216</v>
+        <v>-3.3952</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.0758</v>
+        <v>-2.3551</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.4982</v>
+        <v>-1.4833</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.221</v>
+        <v>-0.3152</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.2771</v>
+        <v>-1.1681</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.5029999999999999</v>
+        <v>-0.2822</v>
       </c>
       <c r="K14" t="n">
-        <v>0.5235</v>
+        <v>0.6005</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.0265</v>
+        <v>-0.8825999999999998</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.9950999999999999</v>
+        <v>-1.2011</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.7444999999999999</v>
+        <v>-0.9156</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2506</v>
+        <v>-0.2855</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.4001</v>
+        <v>-0.3894</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R14" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.4396</v>
+        <v>-2.377</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.218</v>
+        <v>-1.1656</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.2216</v>
+        <v>-1.2114</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.4596</v>
+        <v>-1.5006</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.4596</v>
+        <v>-1.5006</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>3.820199999999999</v>
+        <v>3.731</v>
       </c>
       <c r="E15" t="n">
-        <v>-10.7872</v>
+        <v>-6.5861</v>
       </c>
       <c r="F15" t="n">
-        <v>14.6071</v>
+        <v>10.3169</v>
       </c>
       <c r="G15" t="n">
-        <v>13.1012</v>
+        <v>13.0594</v>
       </c>
       <c r="H15" t="n">
-        <v>6.4584</v>
+        <v>6.283299999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>6.643099999999999</v>
+        <v>6.776199999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>6.642500000000001</v>
+        <v>9.306600000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>14.5118</v>
+        <v>16.2226</v>
       </c>
       <c r="L15" t="n">
-        <v>-7.869400000000001</v>
+        <v>-6.916</v>
       </c>
       <c r="M15" t="n">
-        <v>6.4591</v>
+        <v>3.7532</v>
       </c>
       <c r="N15" t="n">
-        <v>-8.0535</v>
+        <v>-9.939</v>
       </c>
       <c r="O15" t="n">
-        <v>14.5124</v>
+        <v>13.6921</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.0001</v>
+        <v>-0.9734</v>
       </c>
       <c r="Q15" t="n">
-        <v>-25.00729999999999</v>
+        <v>-24.3421</v>
       </c>
       <c r="R15" t="n">
-        <v>24.0067</v>
+        <v>23.3684</v>
       </c>
       <c r="S15" t="n">
-        <v>-6.202299999999999</v>
+        <v>-6.119199999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>-2.998</v>
+        <v>-2.510000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-3.2043</v>
+        <v>-3.6088</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.0783</v>
+        <v>-2.236</v>
       </c>
       <c r="W15" t="n">
-        <v>10.576</v>
+        <v>10.9597</v>
       </c>
       <c r="X15" t="n">
-        <v>-12.6544</v>
+        <v>-13.1953</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_ZENTRO BASKET MADRID.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_ZENTRO BASKET MADRID.xlsx
@@ -565,13 +565,13 @@
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>13.0654</v>
+        <v>10.0586</v>
       </c>
       <c r="E2" t="n">
-        <v>9.3726</v>
+        <v>7.4787</v>
       </c>
       <c r="F2" t="n">
-        <v>3.6928</v>
+        <v>2.5799</v>
       </c>
       <c r="G2" t="n">
         <v>4.5343</v>
@@ -610,13 +610,13 @@
         <v>1.9474</v>
       </c>
       <c r="S2" t="n">
-        <v>4.8037</v>
+        <v>1.7969</v>
       </c>
       <c r="T2" t="n">
-        <v>2.4412</v>
+        <v>0.5473</v>
       </c>
       <c r="U2" t="n">
-        <v>2.3626</v>
+        <v>1.2496</v>
       </c>
       <c r="V2" t="n">
         <v>1.78</v>
@@ -643,13 +643,13 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5444</v>
+        <v>3.1038</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4772</v>
+        <v>1.8758</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0672</v>
+        <v>1.228</v>
       </c>
       <c r="G3" t="n">
         <v>2.2167</v>
@@ -688,13 +688,13 @@
         <v>0.779</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2565</v>
+        <v>0.303</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.04340000000000002</v>
+        <v>0.3554</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2131</v>
+        <v>-0.05239999999999999</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. RUBIO CORCHADO</t>
+          <t>L. SCHIEBELHUT LUIS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2298</v>
+        <v>2.5262</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7176999999999998</v>
+        <v>-0.7199</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5122</v>
+        <v>3.246</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4491</v>
+        <v>3.3993</v>
       </c>
       <c r="H4" t="n">
-        <v>1.2643</v>
+        <v>5.0328</v>
       </c>
       <c r="I4" t="n">
-        <v>1.1848</v>
+        <v>-1.6336</v>
       </c>
       <c r="J4" t="n">
-        <v>1.3553</v>
+        <v>1.8819</v>
       </c>
       <c r="K4" t="n">
-        <v>2.5299</v>
+        <v>5.0906</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.1746</v>
+        <v>-3.2087</v>
       </c>
       <c r="M4" t="n">
-        <v>1.0937</v>
+        <v>1.5175</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.2656</v>
+        <v>-0.05769999999999997</v>
       </c>
       <c r="O4" t="n">
-        <v>2.3594</v>
+        <v>1.5751</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.5842000000000001</v>
+        <v>0.779</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.9211</v>
+        <v>-2.1421</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3368</v>
+        <v>2.921</v>
       </c>
       <c r="S4" t="n">
-        <v>2.476</v>
+        <v>-1.6521</v>
       </c>
       <c r="T4" t="n">
-        <v>2.2834</v>
+        <v>-0.4596000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1927</v>
+        <v>-1.1925</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.1111</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.1111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. SCHIEBELHUT LUIS</t>
+          <t>M. ESTAPE ROIZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6898</v>
+        <v>1.5288</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.6441000000000003</v>
+        <v>1.5246</v>
       </c>
       <c r="F5" t="n">
-        <v>2.334</v>
+        <v>0.004200000000000093</v>
       </c>
       <c r="G5" t="n">
-        <v>3.3993</v>
+        <v>4.259</v>
       </c>
       <c r="H5" t="n">
-        <v>5.0328</v>
+        <v>2.5314</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.6336</v>
+        <v>1.7277</v>
       </c>
       <c r="J5" t="n">
-        <v>1.8819</v>
+        <v>4.9772</v>
       </c>
       <c r="K5" t="n">
-        <v>5.0906</v>
+        <v>4.2799</v>
       </c>
       <c r="L5" t="n">
-        <v>-3.2087</v>
+        <v>0.6972999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>1.5175</v>
+        <v>-0.7181000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.05769999999999997</v>
+        <v>-1.7485</v>
       </c>
       <c r="O5" t="n">
-        <v>1.5751</v>
+        <v>1.0304</v>
       </c>
       <c r="P5" t="n">
-        <v>0.779</v>
+        <v>-3.1157</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.1421</v>
+        <v>-4.868399999999999</v>
       </c>
       <c r="R5" t="n">
-        <v>2.921</v>
+        <v>1.7526</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.4884</v>
+        <v>-0.04869999999999997</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3838999999999999</v>
+        <v>0.1948</v>
       </c>
       <c r="U5" t="n">
-        <v>-2.1044</v>
+        <v>-0.2434000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.4342</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.2211</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.7868000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. ESTAPE ROIZ</t>
+          <t>M. RUBIO CORCHADO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9129</v>
+        <v>0.8900000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>1.4249</v>
+        <v>-0.5542000000000002</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.512</v>
+        <v>1.4441</v>
       </c>
       <c r="G7" t="n">
-        <v>4.259</v>
+        <v>2.4491</v>
       </c>
       <c r="H7" t="n">
-        <v>2.5314</v>
+        <v>1.2643</v>
       </c>
       <c r="I7" t="n">
-        <v>1.7277</v>
+        <v>1.1848</v>
       </c>
       <c r="J7" t="n">
-        <v>4.9772</v>
+        <v>1.3553</v>
       </c>
       <c r="K7" t="n">
-        <v>4.2799</v>
+        <v>2.5299</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6972999999999999</v>
+        <v>-1.1746</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7181000000000001</v>
+        <v>1.0937</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.7485</v>
+        <v>-1.2656</v>
       </c>
       <c r="O7" t="n">
-        <v>1.0304</v>
+        <v>2.3594</v>
       </c>
       <c r="P7" t="n">
-        <v>-3.1157</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.868399999999999</v>
+        <v>-2.9211</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7526</v>
+        <v>2.3368</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6646000000000001</v>
+        <v>1.1361</v>
       </c>
       <c r="T7" t="n">
-        <v>0.09509999999999999</v>
+        <v>1.0116</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7596999999999999</v>
+        <v>0.1246</v>
       </c>
       <c r="V7" t="n">
-        <v>0.4342</v>
+        <v>-2.1111</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2211</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-2.1111</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1084</v>
+        <v>-0.4577</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.0432</v>
+        <v>-1.782</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9347</v>
+        <v>1.3243</v>
       </c>
       <c r="G8" t="n">
         <v>0.2424</v>
@@ -1078,13 +1078,13 @@
         <v>0.5842000000000001</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9613</v>
+        <v>-0.3106</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5565</v>
+        <v>-0.2953</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4048</v>
+        <v>-0.01520000000000001</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. GOMA</t>
+          <t>B. SCHUCH</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6463</v>
+        <v>-0.6820999999999997</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.9801</v>
+        <v>-2.2105</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3336999999999999</v>
+        <v>1.5285</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7081999999999999</v>
+        <v>2.6598</v>
       </c>
       <c r="H9" t="n">
-        <v>-4.2399</v>
+        <v>1.3659</v>
       </c>
       <c r="I9" t="n">
-        <v>3.5317</v>
+        <v>1.2939</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6546999999999999</v>
+        <v>1.5238</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.6243</v>
+        <v>2.317</v>
       </c>
       <c r="L9" t="n">
-        <v>1.9697</v>
+        <v>-0.7932000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.05360000000000001</v>
+        <v>1.136</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.6156</v>
+        <v>-0.9510999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>1.562</v>
+        <v>2.0871</v>
       </c>
       <c r="P9" t="n">
-        <v>0.779</v>
+        <v>-2.921</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.1421</v>
+        <v>-5.0631</v>
       </c>
       <c r="R9" t="n">
-        <v>2.921</v>
+        <v>2.1421</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9300999999999999</v>
+        <v>-1.0313</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6839000000000001</v>
+        <v>-0.4512999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2463</v>
+        <v>-0.5800999999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.7869000000000002</v>
+        <v>0.6104999999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>1.5006</v>
+        <v>1.78</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.2873</v>
+        <v>-1.1695</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B. SCHUCH</t>
+          <t>J. VAQUERO PASCUAL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9625</v>
+        <v>-0.7667999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.1695</v>
+        <v>-2.9343</v>
       </c>
       <c r="F10" t="n">
-        <v>1.207</v>
+        <v>2.1675</v>
       </c>
       <c r="G10" t="n">
-        <v>2.6598</v>
+        <v>-1.1993</v>
       </c>
       <c r="H10" t="n">
-        <v>1.3659</v>
+        <v>-0.3273999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>1.2939</v>
+        <v>-0.8719</v>
       </c>
       <c r="J10" t="n">
-        <v>1.5238</v>
+        <v>-0.5482</v>
       </c>
       <c r="K10" t="n">
-        <v>2.317</v>
+        <v>2.158</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7932000000000001</v>
+        <v>-2.7063</v>
       </c>
       <c r="M10" t="n">
-        <v>1.136</v>
+        <v>-0.651</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.9510999999999999</v>
+        <v>-2.4854</v>
       </c>
       <c r="O10" t="n">
-        <v>2.0871</v>
+        <v>1.8344</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.921</v>
+        <v>2.1421</v>
       </c>
       <c r="Q10" t="n">
-        <v>-5.0631</v>
+        <v>-0.9737</v>
       </c>
       <c r="R10" t="n">
-        <v>2.1421</v>
+        <v>3.1158</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.3118</v>
+        <v>-0.7681</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.4102</v>
+        <v>-0.7503000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9015000000000001</v>
+        <v>-0.0178</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6104999999999999</v>
+        <v>-0.9416</v>
       </c>
       <c r="W10" t="n">
-        <v>1.78</v>
+        <v>-0.6621</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.1695</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E. MARCIEL</t>
+          <t>G. GOMA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.383</v>
+        <v>-1.9857</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.5821</v>
+        <v>-2.2173</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8008999999999999</v>
+        <v>0.2316</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1853000000000002</v>
+        <v>-0.7081999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.239</v>
+        <v>-4.2399</v>
       </c>
       <c r="I11" t="n">
-        <v>3.0538</v>
+        <v>3.5317</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.5011000000000001</v>
+        <v>-0.6546999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.9601</v>
+        <v>-2.6243</v>
       </c>
       <c r="L11" t="n">
-        <v>1.459</v>
+        <v>1.9697</v>
       </c>
       <c r="M11" t="n">
-        <v>0.316</v>
+        <v>-0.05360000000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.2788</v>
+        <v>-1.6156</v>
       </c>
       <c r="O11" t="n">
-        <v>1.5948</v>
+        <v>1.562</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.3895000000000001</v>
+        <v>0.779</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1684</v>
+        <v>-2.1421</v>
       </c>
       <c r="R11" t="n">
-        <v>0.779</v>
+        <v>2.921</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-1.2695</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.192</v>
+        <v>-0.921</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3953</v>
+        <v>-0.3484</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.221</v>
+        <v>-0.7869000000000002</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2795</v>
+        <v>1.5006</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.5005</v>
+        <v>-2.2873</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. VAQUERO PASCUAL</t>
+          <t>E. MARCIEL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.5302</v>
+        <v>-2.1057</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.3917</v>
+        <v>-1.6199</v>
       </c>
       <c r="F12" t="n">
-        <v>1.8614</v>
+        <v>-0.4856999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.1993</v>
+        <v>-0.1853000000000002</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3273999999999999</v>
+        <v>-3.239</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.8719</v>
+        <v>3.0538</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.5482</v>
+        <v>-0.5011000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>2.158</v>
+        <v>-1.9601</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.7063</v>
+        <v>1.459</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.651</v>
+        <v>0.316</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.4854</v>
+        <v>-1.2788</v>
       </c>
       <c r="O12" t="n">
-        <v>1.8344</v>
+        <v>1.5948</v>
       </c>
       <c r="P12" t="n">
-        <v>2.1421</v>
+        <v>-0.3895000000000001</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9737</v>
+        <v>-1.1684</v>
       </c>
       <c r="R12" t="n">
-        <v>3.1158</v>
+        <v>0.779</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.5315</v>
+        <v>-0.3099000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.2076</v>
+        <v>-0.2298</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3238</v>
+        <v>-0.0801</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.9416</v>
+        <v>-1.221</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.6621</v>
+        <v>0.2795</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.2795</v>
+        <v>-1.5005</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.5544</v>
+        <v>-2.2554</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.5963</v>
+        <v>-3.2355</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0419</v>
+        <v>0.98</v>
       </c>
       <c r="G13" t="n">
         <v>-4.348800000000001</v>
@@ -1468,13 +1468,13 @@
         <v>2.5316</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2905</v>
+        <v>0.008500000000000008</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6866</v>
+        <v>-0.3258</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3962</v>
+        <v>0.3343</v>
       </c>
       <c r="V13" t="n">
         <v>1.5005</v>
@@ -1501,13 +1501,13 @@
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.7502</v>
+        <v>-4.7348</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.3952</v>
+        <v>-2.797</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.3551</v>
+        <v>-1.9378</v>
       </c>
       <c r="G14" t="n">
         <v>-1.4833</v>
@@ -1546,13 +1546,13 @@
         <v>1.5579</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.377</v>
+        <v>-1.3615</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1656</v>
+        <v>-0.5676</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.2114</v>
+        <v>-0.7939000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-1.5006</v>
@@ -1579,25 +1579,25 @@
         <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>3.731</v>
+        <v>6.342899999999998</v>
       </c>
       <c r="E15" t="n">
-        <v>-6.5861</v>
+        <v>-5.9678</v>
       </c>
       <c r="F15" t="n">
-        <v>10.3169</v>
+        <v>12.3106</v>
       </c>
       <c r="G15" t="n">
         <v>13.0594</v>
       </c>
       <c r="H15" t="n">
-        <v>6.283299999999999</v>
+        <v>6.283299999999997</v>
       </c>
       <c r="I15" t="n">
         <v>6.776199999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>9.306600000000001</v>
+        <v>9.3066</v>
       </c>
       <c r="K15" t="n">
         <v>16.2226</v>
@@ -1606,7 +1606,7 @@
         <v>-6.916</v>
       </c>
       <c r="M15" t="n">
-        <v>3.7532</v>
+        <v>3.753199999999999</v>
       </c>
       <c r="N15" t="n">
         <v>-9.939</v>
@@ -1624,13 +1624,13 @@
         <v>23.3684</v>
       </c>
       <c r="S15" t="n">
-        <v>-6.119199999999999</v>
+        <v>-3.5072</v>
       </c>
       <c r="T15" t="n">
-        <v>-2.510000000000001</v>
+        <v>-1.8916</v>
       </c>
       <c r="U15" t="n">
-        <v>-3.6088</v>
+        <v>-1.6153</v>
       </c>
       <c r="V15" t="n">
         <v>-2.236</v>
